--- a/AAII_Financials/Yearly/TM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>TM</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>318763300</v>
+      </c>
+      <c r="E8" s="3">
         <v>320783600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>298141100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>279494300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>258407900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>246065500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>277565000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>272770300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>276630200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>186005100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>208762900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>232310500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>235337900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200563500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>167996200</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>246164700</v>
+      </c>
+      <c r="E9" s="3">
         <v>237132800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>222145500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>219120500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>199703400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>191682500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>214713400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>211077500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>212800500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>153229400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>166150200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>186309500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>190538400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>169446600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>148152600</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>53265100</v>
+      </c>
+      <c r="E10" s="3">
         <v>63892200</v>
       </c>
-      <c r="E10" s="3">
-        <v>61948900</v>
-      </c>
       <c r="F10" s="3">
+        <v>61937200</v>
+      </c>
+      <c r="G10" s="3">
         <v>47452100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>49176400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>43692700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>50010200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>49128200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>51695800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>32775700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>42612700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>46001000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>44799500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>31116900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19843600</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,37 +899,38 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>10532100</v>
+      </c>
+      <c r="E12" s="3">
         <v>9940500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9011700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>10578200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>10641100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9859000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10185900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9465600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10020900</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,9 +998,12 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1006,15 +1025,15 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>3085300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>26700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1030,39 +1049,42 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11578300</v>
+      </c>
+      <c r="E15" s="3">
         <v>12305300</v>
       </c>
-      <c r="E15" s="3">
-        <v>11072200</v>
-      </c>
       <c r="F15" s="3">
+        <v>11931400</v>
+      </c>
+      <c r="G15" s="3">
         <v>14711900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>15003000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13487900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13434400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>16175200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>16327200</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>295041400</v>
+      </c>
+      <c r="E17" s="3">
         <v>288828100</v>
       </c>
-      <c r="E17" s="3">
-        <v>262739300</v>
-      </c>
       <c r="F17" s="3">
+        <v>262750900</v>
+      </c>
+      <c r="G17" s="3">
         <v>259032900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>233738500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>226194100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>255267700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>250595400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>254033700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>172563000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>187786200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>208848200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>214342200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>188556600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>164781400</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>23721800</v>
+      </c>
+      <c r="E18" s="3">
         <v>31955500</v>
       </c>
-      <c r="E18" s="3">
-        <v>35401800</v>
-      </c>
       <c r="F18" s="3">
+        <v>35390100</v>
+      </c>
+      <c r="G18" s="3">
         <v>20461400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>24669500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>19871300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>22297300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>22174900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>22596500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13442100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>20976700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>23462300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20995700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12006900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3214900</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6313000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-8202800</v>
       </c>
-      <c r="E20" s="3">
-        <v>-7227900</v>
-      </c>
       <c r="F20" s="3">
+        <v>-7239500</v>
+      </c>
+      <c r="G20" s="3">
         <v>-4909700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6842700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5267600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1912200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3003300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5099000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1542200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1211400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1408600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1544400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>961100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>905500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>41613100</v>
+      </c>
+      <c r="E21" s="3">
         <v>52463700</v>
       </c>
-      <c r="E21" s="3">
-        <v>53701900</v>
-      </c>
       <c r="F21" s="3">
+        <v>54561100</v>
+      </c>
+      <c r="G21" s="3">
         <v>40083000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>46515200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>38626800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>37643900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>41353400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>44022700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>25890400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>34024200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>37031200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>34048000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>23035500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>13784200</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>379200</v>
+      </c>
+      <c r="E22" s="3">
         <v>561700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>428000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>356200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>267300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>383600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>410000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>253400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>259700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>197800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>260200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>195100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>179800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>208800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>207200</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>32407800</v>
+      </c>
+      <c r="E23" s="3">
         <v>42835900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>46048600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>27598200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>32861700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>26513400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>25956200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23874500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>29099500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14786400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21927900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>24675800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22360300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12759200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3913200</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7340900</v>
+      </c>
+      <c r="E24" s="3">
         <v>10850500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>12519700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8844700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9189500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5876900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6336500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5955600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4749400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4238800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6455300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7621300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7033100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5014800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2370900</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>25066900</v>
+      </c>
+      <c r="E26" s="3">
         <v>31985400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>33528900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18753400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23672200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>20636500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19619800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17918800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>24350100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10547600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>15472600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>17054500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>15327200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7744300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1542200</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>24201100</v>
+      </c>
+      <c r="E27" s="3">
         <v>31820700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>32692700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18440100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23470400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>20300900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18922900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16858500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>23367000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12275700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16953600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18538600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16699800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8746100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2563400</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6313000</v>
+      </c>
+      <c r="E32" s="3">
         <v>8202800</v>
       </c>
-      <c r="E32" s="3">
-        <v>7227900</v>
-      </c>
       <c r="F32" s="3">
+        <v>7239500</v>
+      </c>
+      <c r="G32" s="3">
         <v>4909700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6842700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5267600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1912200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3003300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5099000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1542200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1211400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1408600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1544400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-961100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-905500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>24201100</v>
+      </c>
+      <c r="E33" s="3">
         <v>31820700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>32692700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18440100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23470400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>20300900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18922900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16991900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>23482700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12275700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16953600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18538600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16699800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8746100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2563400</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>24201100</v>
+      </c>
+      <c r="E35" s="3">
         <v>31820700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>32692700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18440100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23470400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>20300900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18922900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16991900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>23482700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12275700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16953600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18538600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16699800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8746100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2563400</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,421 +2158,446 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>62168500</v>
+      </c>
+      <c r="E41" s="3">
         <v>40674700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>45570800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>41738000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>35406200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>29603800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>24929200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25180100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>22508600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20186800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>21604800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>19487300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>18697100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15619300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15180000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>45895900</v>
+        <v>25046000</v>
       </c>
       <c r="E42" s="3">
+        <v>46316200</v>
+      </c>
+      <c r="F42" s="3">
         <v>30975300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12590500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>20516400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>38038000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>982500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>20845300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>23485500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>19574700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>18694200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>25005000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>20400100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>14111000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>11402800</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25354000</v>
+      </c>
+      <c r="E43" s="3">
         <v>26018700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25826000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>28622000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27230900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27768800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>26820800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>26539900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25506300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>58971300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>61477200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>75057400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>73429700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>68375100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>58970400</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>32294600</v>
+      </c>
+      <c r="E44" s="3">
         <v>30706500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>30447700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>32013000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>31468600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>26112600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>23548700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23972500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23914000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>16099300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15152100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>18233900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>17355500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>15596500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>14665400</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8519200</v>
+        <v>22245400</v>
       </c>
       <c r="E45" s="3">
+        <v>8098800</v>
+      </c>
+      <c r="F45" s="3">
         <v>6929400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6987300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6652300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6813400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>25256800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>96700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>328800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5367000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16912000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15213900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14091700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11602800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>11165000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>269325400</v>
+      </c>
+      <c r="E46" s="3">
         <v>247607200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>229508300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>199044500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>195351300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>205940400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>176235800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>170374800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>170920900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>120199000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>133840000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>152998000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>143974000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>125305000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>111384000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>38718700</v>
+        <v>103634100</v>
       </c>
       <c r="E47" s="3">
+        <v>104715200</v>
+      </c>
+      <c r="F47" s="3">
         <v>37751500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>118733900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>118213700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>119754400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>39939400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>98441400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>106760900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>131855000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>137793000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>166943000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>158854000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>129781000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>105167000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>65947500</v>
+      </c>
+      <c r="E48" s="3">
         <v>64895200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>60914100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>61838000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>63824200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>65057600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>61016700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>55757600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>55571400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>68728500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>71592100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>79292500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>69994300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>62277800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>56367800</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>9103700</v>
+        <v>5467200</v>
       </c>
       <c r="E49" s="3">
+        <v>5213200</v>
+      </c>
+      <c r="F49" s="3">
         <v>8960500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9396600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9815800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10023900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9295900</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>8</v>
@@ -2498,15 +2608,18 @@
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>71820300</v>
+        <v>5124200</v>
       </c>
       <c r="E52" s="3">
+        <v>5823800</v>
+      </c>
+      <c r="F52" s="3">
         <v>82011500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6068300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5920700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4972400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>75237500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>6145100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5401200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7794200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5367500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7902100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6745300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5179600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4166100</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>663641600</v>
+      </c>
+      <c r="E54" s="3">
         <v>625059100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>595777300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>558947900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>557412000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>562999100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>501592600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>468702700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>473690000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>328576000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>348593000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>407135000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>379567000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>322543000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>277085000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27055800</v>
+      </c>
+      <c r="E57" s="3">
         <v>26944700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>25308700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28731100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>26088900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26706500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>21880900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>23878600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24355300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17297400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17562900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20562300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20273100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>19214200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>20273000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>106727600</v>
+        <v>111597400</v>
       </c>
       <c r="E58" s="3">
+        <v>106323000</v>
+      </c>
+      <c r="F58" s="3">
         <v>102944400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>92923400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>92855100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>111228300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>92780100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>86888800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>88281200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>62305400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>62630000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>76458600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>71269200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>61757100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>53908000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>50337000</v>
+        <v>59048300</v>
       </c>
       <c r="E59" s="3">
+        <v>50741600</v>
+      </c>
+      <c r="F59" s="3">
         <v>52073400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>46577600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>47325600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>42674100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>42123800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>40423600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>41426200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>37127000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>38321800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>43139800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>42932800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>36403500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>32324500</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>211345700</v>
+      </c>
+      <c r="E60" s="3">
         <v>196558400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>192905400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>180237700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>179868600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>194038500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>168604800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>164488200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>167571100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>116730000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>118515000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>140161000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>134475000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>117375000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>106505000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14235800</v>
+        <v>14258200</v>
       </c>
       <c r="E61" s="3">
+        <v>12612500</v>
+      </c>
+      <c r="F61" s="3">
         <v>16358700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13765300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>14428000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>14729000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16368400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6909000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5565500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>66804200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>71824700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>85422800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>78289700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>66700800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>54622200</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6421200</v>
+        <v>13322300</v>
       </c>
       <c r="E62" s="3">
+        <v>8044500</v>
+      </c>
+      <c r="F62" s="3">
         <v>3758200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5668800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5596100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5081600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4583600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8343200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8160700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>19213500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>25305200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>31020300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>27396600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>22362500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15916100</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>405661900</v>
+      </c>
+      <c r="E66" s="3">
         <v>378785900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>362797600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>338807000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>333794100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>343392000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>303278300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>287607700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>290741000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>207252000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>221977000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>263933000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>247030000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>212118000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>181710000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3411,14 +3578,14 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>3274800</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>3526400</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>243450600</v>
+      </c>
+      <c r="E72" s="3">
         <v>239343600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>216821700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>213213300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>217839500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>217942100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>206632400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>198425400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>183357300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>118631000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>123438000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>132999000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>129305000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>115345000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>107730000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>251054100</v>
+      </c>
+      <c r="E76" s="3">
         <v>239901900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>226247000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>213178800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>216133600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>211616300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>191621800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>174606600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>176413400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>118050000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>123090000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>143203000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>132537000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>110426000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>95374400</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>24201100</v>
+      </c>
+      <c r="E81" s="3">
         <v>31820700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>32692700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18440100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23470400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>20300900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18922900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16991900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>23482700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12275700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16953600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18538600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16699800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8746100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2563400</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>12973700</v>
+      </c>
+      <c r="E83" s="3">
         <v>12978700</v>
       </c>
-      <c r="E83" s="3">
-        <v>11876800</v>
-      </c>
       <c r="F83" s="3">
+        <v>12736000</v>
+      </c>
+      <c r="G83" s="3">
         <v>15345200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15003000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13487900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13434400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>16175200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>16327200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10857800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11949900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12019400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11457800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10045400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9653200</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>34419800</v>
+      </c>
+      <c r="E89" s="3">
         <v>24687700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>27809800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>22229600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30655500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>24658100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>22290400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>33991500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>39763900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>23012000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>32787300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>31439500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>33397700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>22282500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>13130000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-30908100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-32746600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-31166600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25257300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-28691800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-31550900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-31984400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-33741400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-33884500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-23869300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-29835200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28640100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-24536800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17945000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-13850000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9561400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-27978600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-33048500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12027700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4755600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-42352800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19745500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-24341100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-34462500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-20017400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23391700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-32529100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-39720000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-27518300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13041600</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>7792000</v>
+      </c>
+      <c r="E96" s="3">
         <v>7561600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>5819300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>5476300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>5845700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>5655700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>5750800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>5819000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>5902700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-4301300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-5188800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-4733600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3627600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1727200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1417300</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3375100</v>
+      </c>
+      <c r="E100" s="3">
         <v>1317100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>16512200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-422600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-20311600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>24766700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3371700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4880800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4228900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2528600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3113200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2610600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>8422400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4338100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-3212300</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2372200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-895400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1255600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>777100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2752100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1991400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1310400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-375800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-410400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-90900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1469100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>555100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>857400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1253100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-505700</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23855500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2869200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12529100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10556400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8340300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9063400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4606300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4393800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>662000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>375100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4813300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2076100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2957500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>355400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3629600</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
